--- a/output/第10期計画_概要版の構成案.xlsx
+++ b/output/第10期計画_概要版の構成案.xlsx
@@ -2803,7 +2803,7 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>地域差指数による給付水準の要因分解</t>
+          <t>地域差指数による給付水準の要素別の比較</t>
         </is>
       </c>
       <c r="D23" s="9" t="n"/>
